--- a/docs/API명세서/API명세서_v12(final).xlsx
+++ b/docs/API명세서/API명세서_v12(final).xlsx
@@ -2403,7 +2403,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>삭제 요청은 notification_logs.deleted_at을 설정한다. 삭제된 기록은 알림함 목록, 확인 처리, 삭제 대상 조회에서 제외하되 감사와 장애 분석을 위해 데이터베이스에 보존한다. 일괄 삭제 요청은 ID 배열과 delete_all 또는 acknowledged_only 조건 중 하나를 사용한다.</t>
+          <t>삭제 요청은 notification_logs.deleted_at을 설정한다. 삭제된 기록은 알림함 목록, 확인 처리, 삭제 대상 조회에서 제외하되 감사와 장애 분석을 위해 데이터베이스에 보존한다. 선택 삭제(POST .../notifications/delete)는 notification_ids 배열만 받고, 확인한 알림 일괄 삭제(DELETE .../notifications)는 파라미터 없이 확인 처리된 알림만 지운다 — 모드를 고르는 조건이 아니라 별도의 두 엔드포인트다.</t>
         </is>
       </c>
     </row>
